--- a/_files/class/Statistical_Analysis_1.xlsx
+++ b/_files/class/Statistical_Analysis_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d01ed0f4ecfdbb64/Working/Teaching/Business analytcis with Excel/Quarto/reimage2/_files/class/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDC59E3-65AC-43EA-8FD2-74CDA5F21722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{7EDC59E3-65AC-43EA-8FD2-74CDA5F21722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C4D6B07-841B-C44F-9F77-9BEF17AC4548}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7F6A2A6D-A672-4771-AB2F-9FBAFA356631}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="1" xr2:uid="{7F6A2A6D-A672-4771-AB2F-9FBAFA356631}"/>
   </bookViews>
   <sheets>
     <sheet name="DESCRIPTIVE" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="42">
   <si>
     <t>MSY</t>
   </si>
@@ -120,18 +120,6 @@
     <t>Observed</t>
   </si>
   <si>
-    <t>(Exp-Observed)^2</t>
-  </si>
-  <si>
-    <t>Divided by Exp</t>
-  </si>
-  <si>
-    <t>Sum</t>
-  </si>
-  <si>
-    <t>Chi Sq Distribution</t>
-  </si>
-  <si>
     <t>SubjectID</t>
   </si>
   <si>
@@ -163,6 +151,21 @@
   </si>
   <si>
     <t>Louis Armstrong New Orleans International Airport</t>
+  </si>
+  <si>
+    <t>Chi squared test</t>
+  </si>
+  <si>
+    <t>&gt;0.05</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>&lt;0.05</t>
+  </si>
+  <si>
+    <t>Not-normal</t>
   </si>
 </sst>
 </file>
@@ -265,9 +268,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -305,7 +308,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -411,7 +414,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -553,7 +556,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -562,22 +565,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C73B6651-D60D-44D3-97CB-D0779FECB401}">
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
@@ -606,7 +609,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -614,7 +617,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D2">
         <v>142</v>
@@ -629,7 +632,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -637,7 +640,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <v>54</v>
@@ -652,7 +655,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -660,7 +663,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D4">
         <v>39</v>
@@ -675,7 +678,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -683,7 +686,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>63</v>
@@ -698,7 +701,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -706,7 +709,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>40</v>
@@ -721,7 +724,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -729,7 +732,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D7">
         <v>107</v>
@@ -744,7 +747,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -752,7 +755,7 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D8">
         <v>187</v>
@@ -767,7 +770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -775,7 +778,7 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D9">
         <v>284</v>
@@ -790,7 +793,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -798,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D10">
         <v>183</v>
@@ -813,7 +816,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -821,7 +824,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D11">
         <v>94</v>
@@ -836,7 +839,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -844,7 +847,7 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D12">
         <v>363</v>
@@ -859,7 +862,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -867,7 +870,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D13">
         <v>104</v>
@@ -882,7 +885,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -890,7 +893,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D14">
         <v>127</v>
@@ -905,7 +908,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -913,7 +916,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D15">
         <v>116</v>
@@ -928,7 +931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -936,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D16">
         <v>300</v>
@@ -951,7 +954,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -959,7 +962,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D17">
         <v>35</v>
@@ -974,7 +977,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -982,7 +985,7 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D18">
         <v>111</v>
@@ -997,7 +1000,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -1005,7 +1008,7 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D19">
         <v>291</v>
@@ -1020,7 +1023,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -1028,7 +1031,7 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D20">
         <v>107</v>
@@ -1043,7 +1046,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>1</v>
       </c>
@@ -1051,7 +1054,7 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D21">
         <v>160</v>
@@ -1066,7 +1069,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1074,7 +1077,7 @@
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D22">
         <v>316</v>
@@ -1089,7 +1092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1097,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D23">
         <v>79</v>
@@ -1112,7 +1115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>1</v>
       </c>
@@ -1120,7 +1123,7 @@
         <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D24">
         <v>183</v>
@@ -1135,7 +1138,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>1</v>
       </c>
@@ -1143,7 +1146,7 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D25">
         <v>111</v>
@@ -1158,7 +1161,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1166,7 +1169,7 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D26">
         <v>107</v>
@@ -1181,7 +1184,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1189,7 +1192,7 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D27">
         <v>151</v>
@@ -1204,7 +1207,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>1</v>
       </c>
@@ -1212,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D28">
         <v>36</v>
@@ -1227,7 +1230,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -1235,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D29">
         <v>78</v>
@@ -1257,10 +1260,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CABE8EBB-8851-4F79-8285-DAD26BEA9AF6}">
-  <dimension ref="A1:Y51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AB51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
@@ -1285,30 +1288,40 @@
       <c r="W1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="X1" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="X1" s="3"/>
       <c r="Y1" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>19.2</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AA2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>20.8</v>
       </c>
       <c r="C3">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AA3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>26.3</v>
       </c>
@@ -1316,7 +1329,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>28.9</v>
       </c>
@@ -1324,7 +1337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>30.7</v>
       </c>
@@ -1332,7 +1345,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>31</v>
       </c>
@@ -1340,7 +1353,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>33.4</v>
       </c>
@@ -1348,7 +1361,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>33.799999999999997</v>
       </c>
@@ -1356,7 +1369,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>34.1</v>
       </c>
@@ -1364,7 +1377,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>34.200000000000003</v>
       </c>
@@ -1372,7 +1385,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>37.6</v>
       </c>
@@ -1380,7 +1393,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>40</v>
       </c>
@@ -1388,7 +1401,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>38.200000000000003</v>
       </c>
@@ -1396,7 +1409,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>40.700000000000003</v>
       </c>
@@ -1404,188 +1417,183 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>41.8</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>42.4</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>43.9</v>
       </c>
-      <c r="X18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>44.8</v>
       </c>
-      <c r="X19" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>45.8</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>47.1</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>47.3</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>47.4</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>47.5</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>48.1</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>48.8</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>49.2</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>49.3</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>50.4</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>51.4</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>51.8</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>51.9</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>52.5</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>52.7</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>53.1</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>53.2</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>53.2</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>54.6</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>55.2</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>56.1</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>57.5</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>58.9</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>60.1</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>60.4</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>61.8</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>61.9</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>71.3</v>
       </c>
@@ -1598,11 +1606,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23914E8E-5EF3-4E8F-87E3-91EAFEC4A91D}">
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>17</v>
@@ -1614,7 +1622,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1629,7 +1637,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>14</v>
       </c>
@@ -1640,7 +1648,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1651,7 +1659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>10</v>
       </c>
@@ -1662,7 +1670,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1673,13 +1681,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -1695,14 +1703,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60AC4061-CDF4-4C9C-8879-CF93C3DE0742}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -1713,7 +1721,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>55</v>
       </c>
@@ -1721,7 +1729,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>58</v>
       </c>
@@ -1729,7 +1737,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>56</v>
       </c>
@@ -1737,7 +1745,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>45</v>
       </c>
@@ -1745,7 +1753,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>62</v>
       </c>
@@ -1753,7 +1761,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>51</v>
       </c>
@@ -1764,7 +1772,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>67</v>
       </c>
@@ -1772,7 +1780,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>52</v>
       </c>
@@ -1780,7 +1788,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>75</v>
       </c>
@@ -1788,7 +1796,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>65.3888888888889</v>
       </c>
@@ -1796,7 +1804,7 @@
         <v>67.8055555555556</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>66.8888888888889</v>
       </c>
@@ -1804,7 +1812,7 @@
         <v>67.322222222222194</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>68.3888888888889</v>
       </c>
@@ -1812,7 +1820,7 @@
         <v>66.838888888888903</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>69.8888888888889</v>
       </c>
@@ -1820,7 +1828,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>71.3888888888889</v>
       </c>
@@ -1828,7 +1836,7 @@
         <v>65.872222222222206</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>72.8888888888889</v>
       </c>
@@ -1836,7 +1844,7 @@
         <v>65.3888888888889</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>74.3888888888889</v>
       </c>
@@ -1852,23 +1860,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E56126A-DC52-43CF-AF1A-88E452E20FDA}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1879,7 +1887,7 @@
         <v>110.64</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1890,7 +1898,7 @@
         <v>101.58</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1901,7 +1909,7 @@
         <v>120.6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1912,7 +1920,7 @@
         <v>83.22</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1923,7 +1931,7 @@
         <v>109.27</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1934,7 +1942,7 @@
         <v>115.8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1945,7 +1953,7 @@
         <v>99.89</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1956,7 +1964,7 @@
         <v>117.94</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1967,7 +1975,7 @@
         <v>106.05</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1978,7 +1986,7 @@
         <v>82.82</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1989,7 +1997,7 @@
         <v>116.63</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2000,7 +2008,7 @@
         <v>128.61000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2011,7 +2019,7 @@
         <v>119.66</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2022,7 +2030,7 @@
         <v>108.38</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2041,13 +2049,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01BC7A64-394A-4EAA-B61F-AF963CEF272A}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -2059,7 +2067,7 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>55</v>
       </c>
@@ -2067,7 +2075,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>58</v>
       </c>
@@ -2075,7 +2083,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>56</v>
       </c>
@@ -2083,7 +2091,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>45</v>
       </c>
@@ -2091,7 +2099,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>62</v>
       </c>
@@ -2104,7 +2112,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>68</v>
       </c>
@@ -2112,7 +2120,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>67</v>
       </c>
@@ -2120,7 +2128,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>52</v>
       </c>
@@ -2128,7 +2136,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>75</v>
       </c>
@@ -2136,7 +2144,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>65.3888888888889</v>
       </c>
@@ -2144,7 +2152,7 @@
         <v>55.6666666666667</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>66.8888888888889</v>
       </c>
@@ -2159,7 +2167,7 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>68.3888888888889</v>
       </c>
@@ -2168,7 +2176,7 @@
       </c>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>69.8888888888889</v>
       </c>
@@ -2176,7 +2184,7 @@
         <v>69.8888888888889</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>71.3888888888889</v>
       </c>
@@ -2184,7 +2192,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>72.8888888888889</v>
       </c>
@@ -2192,7 +2200,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>74.3888888888889</v>
       </c>
@@ -2209,9 +2217,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C21C70D-EC4F-4E42-A238-B4DF968E5234}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -2225,10 +2233,10 @@
         <v>6</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>55</v>
       </c>
@@ -2242,7 +2250,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>58</v>
       </c>
@@ -2256,7 +2264,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>56</v>
       </c>
@@ -2270,7 +2278,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>45</v>
       </c>
@@ -2284,7 +2292,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>62</v>
       </c>
@@ -2298,7 +2306,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>68</v>
       </c>
@@ -2312,7 +2320,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>67</v>
       </c>
@@ -2326,7 +2334,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>52</v>
       </c>
@@ -2340,7 +2348,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>75</v>
       </c>
@@ -2354,7 +2362,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>65.3888888888889</v>
       </c>
@@ -2368,7 +2376,7 @@
         <v>65.3888888888889</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>66.8888888888889</v>
       </c>
@@ -2382,7 +2390,7 @@
         <v>66.8888888888889</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>68.3888888888889</v>
       </c>
@@ -2396,7 +2404,7 @@
         <v>68.3888888888889</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>69.8888888888889</v>
       </c>
@@ -2410,7 +2418,7 @@
         <v>69.8888888888889</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>71.3888888888889</v>
       </c>
@@ -2424,7 +2432,7 @@
         <v>71.3888888888889</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>72.8888888888889</v>
       </c>
@@ -2438,7 +2446,7 @@
         <v>72.8888888888889</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>74.3888888888889</v>
       </c>
